--- a/ig/DM-FEVRIER-2026/ValueSet-jdv-j323-activite-sociale-regulee-finess.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-jdv-j323-activite-sociale-regulee-finess.xlsx
@@ -42,13 +42,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>JdvJ323ActiviteSocialeRegulee</t>
+    <t>JdvJ323ActiviteSocialeReguleeFiness</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Jdv J323 Activite Sociale Regulee</t>
+    <t>Jdv J323 Activite Sociale Regulee Finess</t>
   </si>
   <si>
     <t>Status</t>
